--- a/dcf/NVDA.xlsx
+++ b/dcf/NVDA.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1165,25 +1165,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>130.7596532875095</v>
+        <v>107.2961151039063</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>126.3483912913086</v>
+        <v>103.8073895120135</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>122.1267860735824</v>
+        <v>100.4669553508456</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>118.0855932592117</v>
+        <v>97.26762170754587</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>114.2160639845011</v>
+        <v>94.20258206327468</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>110.5099161203828</v>
+        <v>91.26539200515805</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>106.9593072896334</v>
+        <v>88.449948326325</v>
       </c>
     </row>
     <row r="6">
@@ -1191,25 +1191,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>138.3271440416706</v>
+        <v>113.1340000850605</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>133.5891752295979</v>
+        <v>109.3932389274063</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>129.056311479863</v>
+        <v>105.8126866652325</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>124.7185149628685</v>
+        <v>102.3845402810714</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>120.5662873211908</v>
+        <v>99.10141506466969</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>116.590638280984</v>
+        <v>95.95632031008211</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>112.7830562229471</v>
+        <v>92.94263652856833</v>
       </c>
     </row>
     <row r="7">
@@ -1217,25 +1217,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>145.8946347958316</v>
+        <v>118.9718850662147</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>140.8299591678872</v>
+        <v>114.9790883427992</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>135.9858368861437</v>
+        <v>111.1584179796194</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>131.3514366665253</v>
+        <v>107.501458854597</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>126.9165106578806</v>
+        <v>104.0002480660647</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>122.6713604415853</v>
+        <v>100.6472486150062</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>118.6068051562608</v>
+        <v>97.43532473081166</v>
       </c>
     </row>
     <row r="8">
@@ -1243,25 +1243,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>153.4621255499927</v>
+        <v>124.8097700473689</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>148.0707431061764</v>
+        <v>120.5649377581921</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>142.9153622924244</v>
+        <v>116.5041492940064</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>137.9843583701822</v>
+        <v>112.6183774281225</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>133.2667339945703</v>
+        <v>108.8990810674597</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>128.7520826021865</v>
+        <v>105.3381769199302</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>124.4305540895746</v>
+        <v>101.928012933055</v>
       </c>
     </row>
     <row r="9">
@@ -1269,25 +1269,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>161.0296163041537</v>
+        <v>130.647655028523</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>155.3115270444657</v>
+        <v>126.1507871735849</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>149.844887698705</v>
+        <v>121.8498806083933</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>144.617280073839</v>
+        <v>117.7352960016481</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>139.61695733126</v>
+        <v>113.7979140688547</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>134.8328047627877</v>
+        <v>110.0291052248543</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>130.2543030228883</v>
+        <v>106.4207011352983</v>
       </c>
     </row>
     <row r="10">
@@ -1295,25 +1295,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>168.5971070583148</v>
+        <v>136.4855400096772</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>162.552310982755</v>
+        <v>131.7366365889777</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>156.7744131049857</v>
+        <v>127.1956119227802</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>151.2502017774958</v>
+        <v>122.8522145751737</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>145.9671806679497</v>
+        <v>118.6967470702497</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>140.9135269233889</v>
+        <v>114.7200335297783</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>136.078051956202</v>
+        <v>110.9133893375417</v>
       </c>
     </row>
     <row r="11">
@@ -1321,25 +1321,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>176.1645978124758</v>
+        <v>142.3234249908314</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>169.7930949210443</v>
+        <v>137.3224860043706</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>163.7039385112664</v>
+        <v>132.5413432371671</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>157.8831234811526</v>
+        <v>127.9691331486992</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>152.3174040046395</v>
+        <v>123.5955800716447</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>146.9942490839901</v>
+        <v>119.4109618347024</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>141.9018008895157</v>
+        <v>115.406077539785</v>
       </c>
     </row>
     <row r="13">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.067412282181083</v>
+        <v>1.077726409389355</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24518,7 +24518,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24670,13 +24670,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>137.9843583701822</v>
+        <v>112.6183774281225</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>179.4280451044197</v>
+        <v>142.626001393147</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>105.6457955850039</v>
+        <v>88.59672942037547</v>
       </c>
     </row>
     <row r="59">
